--- a/data/masterdata/Technology_Rules.xlsx
+++ b/data/masterdata/Technology_Rules.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://beotalk-my.sharepoint.com/personal/tora_bang-olufsen_dk/Documents/Dokumenter/GitHub/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FFC832DA-5D1A-4446-AC8D-16159F8AD99C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="8_{FFC832DA-5D1A-4446-AC8D-16159F8AD99C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{508CCE5E-4F6D-4193-94FD-7547F077E198}"/>
   <bookViews>
     <workbookView xWindow="-57720" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{34F0C614-9941-4C4B-8976-11F0999F7F3F}"/>
   </bookViews>
@@ -39,36 +39,50 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
-  <si>
-    <t>Rule ID</t>
-  </si>
-  <si>
-    <t>Attribute</t>
-  </si>
-  <si>
-    <t>Operator</t>
-  </si>
-  <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>Recommended Technology</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+  <si>
+    <t>Technology_ID</t>
+  </si>
+  <si>
+    <t>Technology_Name</t>
+  </si>
+  <si>
+    <t>Material_Group</t>
+  </si>
+  <si>
+    <t>Min_Weight_kg</t>
+  </si>
+  <si>
+    <t>Max_Weight_kg</t>
+  </si>
+  <si>
+    <t>Min_Volume</t>
+  </si>
+  <si>
+    <t>Max_Volume</t>
+  </si>
+  <si>
+    <t>Base_Score</t>
+  </si>
+  <si>
+    <t>CNC</t>
+  </si>
+  <si>
+    <t>CNC Machining</t>
+  </si>
+  <si>
+    <t>Aluminium</t>
+  </si>
+  <si>
+    <t>0.001</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -95,11 +109,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -434,28 +445,67 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D1DFB5D-AA7C-4EFA-829A-D5E820AAF750}">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="10.81640625" customWidth="1"/>
-    <col min="5" max="5" width="40.26953125" customWidth="1"/>
+    <col min="1" max="2" width="16.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="14.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.54296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.08984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2">
+        <v>100</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>5000</v>
+      </c>
+      <c r="H2">
+        <v>85</v>
       </c>
     </row>
   </sheetData>

--- a/data/masterdata/Technology_Rules.xlsx
+++ b/data/masterdata/Technology_Rules.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://beotalk-my.sharepoint.com/personal/tora_bang-olufsen_dk/Documents/Dokumenter/GitHub/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tora\GitHub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="8_{FFC832DA-5D1A-4446-AC8D-16159F8AD99C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{508CCE5E-4F6D-4193-94FD-7547F077E198}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0A8AA556-29B1-4D63-9AE0-468E94F98DA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-57720" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{34F0C614-9941-4C4B-8976-11F0999F7F3F}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="22">
   <si>
     <t>Technology_ID</t>
   </si>
@@ -75,6 +75,36 @@
   </si>
   <si>
     <t>0.001</t>
+  </si>
+  <si>
+    <t>Complexity_Supported</t>
+  </si>
+  <si>
+    <t>All</t>
+  </si>
+  <si>
+    <t>MJF</t>
+  </si>
+  <si>
+    <t>HP Multi Jet Fusion</t>
+  </si>
+  <si>
+    <t>Polymer</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>DC</t>
+  </si>
+  <si>
+    <t>Die Casting</t>
+  </si>
+  <si>
+    <t>0.005</t>
+  </si>
+  <si>
+    <t>Low</t>
   </si>
 </sst>
 </file>
@@ -445,18 +475,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D1DFB5D-AA7C-4EFA-829A-D5E820AAF750}">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="16.90625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.26953125" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="14.26953125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.54296875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.81640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.08984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.81640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -479,10 +511,13 @@
         <v>6</v>
       </c>
       <c r="H1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -504,8 +539,69 @@
       <c r="G2">
         <v>5000</v>
       </c>
-      <c r="H2">
-        <v>85</v>
+      <c r="H2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3">
+        <v>5</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>5000</v>
+      </c>
+      <c r="H3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4">
+        <v>20</v>
+      </c>
+      <c r="F4">
+        <v>5000</v>
+      </c>
+      <c r="G4">
+        <v>1000000</v>
+      </c>
+      <c r="H4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I4">
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/data/masterdata/Technology_Rules.xlsx
+++ b/data/masterdata/Technology_Rules.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tora\GitHub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0A8AA556-29B1-4D63-9AE0-468E94F98DA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C3EAC1F8-60E1-4973-B0A5-8C27CBB046B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-57720" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{34F0C614-9941-4C4B-8976-11F0999F7F3F}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="25">
   <si>
     <t>Technology_ID</t>
   </si>
@@ -105,6 +105,15 @@
   </si>
   <si>
     <t>Low</t>
+  </si>
+  <si>
+    <t>Material_Compatibility</t>
+  </si>
+  <si>
+    <t>Compatible</t>
+  </si>
+  <si>
+    <t>Not Compatible</t>
   </si>
 </sst>
 </file>
@@ -475,7 +484,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D1DFB5D-AA7C-4EFA-829A-D5E820AAF750}">
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.453125" bestFit="1" customWidth="1"/>
@@ -486,9 +495,10 @@
     <col min="7" max="7" width="12.08984375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="20.81640625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10.453125" customWidth="1"/>
+    <col min="10" max="10" width="17.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -516,8 +526,11 @@
       <c r="I1" t="s">
         <v>7</v>
       </c>
+      <c r="J1" t="s">
+        <v>22</v>
+      </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -545,8 +558,11 @@
       <c r="I2">
         <v>20</v>
       </c>
+      <c r="J2" t="s">
+        <v>23</v>
+      </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -574,8 +590,11 @@
       <c r="I3">
         <v>20</v>
       </c>
+      <c r="J3" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -602,6 +621,9 @@
       </c>
       <c r="I4">
         <v>20</v>
+      </c>
+      <c r="J4" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/data/masterdata/Technology_Rules.xlsx
+++ b/data/masterdata/Technology_Rules.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tora\GitHub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C3EAC1F8-60E1-4973-B0A5-8C27CBB046B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{149ACD34-0CA7-4293-8DFE-5E4757FDE16A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-57720" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{34F0C614-9941-4C4B-8976-11F0999F7F3F}"/>
+    <workbookView xWindow="-57705" yWindow="0" windowWidth="14610" windowHeight="17385" xr2:uid="{34F0C614-9941-4C4B-8976-11F0999F7F3F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -120,8 +120,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -148,8 +155,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -498,35 +506,35 @@
     <col min="10" max="10" width="17.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+    <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>22</v>
       </c>
     </row>

--- a/data/masterdata/Technology_Rules.xlsx
+++ b/data/masterdata/Technology_Rules.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tora\GitHub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{149ACD34-0CA7-4293-8DFE-5E4757FDE16A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6328D885-DBB9-484E-9896-EF20F598298C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-57705" yWindow="0" windowWidth="14610" windowHeight="17385" xr2:uid="{34F0C614-9941-4C4B-8976-11F0999F7F3F}"/>
+    <workbookView xWindow="-57975" yWindow="10590" windowWidth="21600" windowHeight="6315" xr2:uid="{34F0C614-9941-4C4B-8976-11F0999F7F3F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="26">
   <si>
     <t>Technology_ID</t>
   </si>
@@ -101,12 +101,6 @@
     <t>Die Casting</t>
   </si>
   <si>
-    <t>0.005</t>
-  </si>
-  <si>
-    <t>Low</t>
-  </si>
-  <si>
     <t>Material_Compatibility</t>
   </si>
   <si>
@@ -114,6 +108,15 @@
   </si>
   <si>
     <t>Not Compatible</t>
+  </si>
+  <si>
+    <t>0.02</t>
+  </si>
+  <si>
+    <t>IM</t>
+  </si>
+  <si>
+    <t>Injection Molding</t>
   </si>
 </sst>
 </file>
@@ -155,9 +158,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -492,11 +498,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D1DFB5D-AA7C-4EFA-829A-D5E820AAF750}">
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.26953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.36328125" customWidth="1"/>
+    <col min="2" max="2" width="25.1796875" customWidth="1"/>
     <col min="3" max="4" width="14.26953125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.54296875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.81640625" bestFit="1" customWidth="1"/>
@@ -535,7 +541,7 @@
         <v>7</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
@@ -567,7 +573,7 @@
         <v>20</v>
       </c>
       <c r="J2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
@@ -599,39 +605,68 @@
         <v>20</v>
       </c>
       <c r="J3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+      <c r="A4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" s="2">
         <v>20</v>
       </c>
-      <c r="E4">
-        <v>20</v>
-      </c>
-      <c r="F4">
-        <v>5000</v>
-      </c>
-      <c r="G4">
-        <v>1000000</v>
-      </c>
-      <c r="H4" t="s">
+      <c r="F4" s="2">
+        <v>10000</v>
+      </c>
+      <c r="G4" s="2">
+        <v>5000000</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="2">
+        <v>30</v>
+      </c>
+      <c r="J4" t="s">
         <v>21</v>
       </c>
-      <c r="I4">
-        <v>20</v>
-      </c>
-      <c r="J4" t="s">
-        <v>23</v>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="2">
+        <v>5</v>
+      </c>
+      <c r="F5" s="2">
+        <v>1000</v>
+      </c>
+      <c r="G5" s="2">
+        <v>10000000</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I5" s="2">
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/data/masterdata/Technology_Rules.xlsx
+++ b/data/masterdata/Technology_Rules.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tora\GitHub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6328D885-DBB9-484E-9896-EF20F598298C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8C0874F-FA03-4194-944A-C6E7FEE97063}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-57975" yWindow="10590" windowWidth="21600" windowHeight="6315" xr2:uid="{34F0C614-9941-4C4B-8976-11F0999F7F3F}"/>
+    <workbookView xWindow="-57720" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{34F0C614-9941-4C4B-8976-11F0999F7F3F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="28">
   <si>
     <t>Technology_ID</t>
   </si>
@@ -117,6 +117,12 @@
   </si>
   <si>
     <t>Injection Molding</t>
+  </si>
+  <si>
+    <t>Injection Moulding</t>
+  </si>
+  <si>
+    <t>Plastic</t>
   </si>
 </sst>
 </file>
@@ -158,9 +164,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -498,7 +507,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D1DFB5D-AA7C-4EFA-829A-D5E820AAF750}">
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="30.36328125" customWidth="1"/>
@@ -609,31 +618,31 @@
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E4" s="2">
+      <c r="E4" s="3">
         <v>20</v>
       </c>
-      <c r="F4" s="2">
+      <c r="F4" s="3">
         <v>10000</v>
       </c>
-      <c r="G4" s="2">
+      <c r="G4" s="3">
         <v>5000000</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="I4" s="2">
+      <c r="I4" s="3">
         <v>30</v>
       </c>
       <c r="J4" t="s">
@@ -641,33 +650,81 @@
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="2">
+      <c r="E5" s="3">
         <v>5</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F5" s="3">
         <v>1000</v>
       </c>
-      <c r="G5" s="2">
+      <c r="G5" s="3">
         <v>10000000</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="H5" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="I5" s="2">
+      <c r="I5" s="3">
         <v>30</v>
       </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="B6" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" s="3">
+        <v>1000</v>
+      </c>
+      <c r="G6" s="3">
+        <v>10000000</v>
+      </c>
+      <c r="I6" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="B7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" s="3">
+        <v>1</v>
+      </c>
+      <c r="F7" s="3">
+        <v>5000</v>
+      </c>
+      <c r="I7" s="3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/masterdata/Technology_Rules.xlsx
+++ b/data/masterdata/Technology_Rules.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tora\GitHub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8C0874F-FA03-4194-944A-C6E7FEE97063}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD46E5A8-A0E6-42BD-BF9F-1C4A63D62629}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-57720" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{34F0C614-9941-4C4B-8976-11F0999F7F3F}"/>
+    <workbookView xWindow="2280" yWindow="2280" windowWidth="14400" windowHeight="8350" xr2:uid="{34F0C614-9941-4C4B-8976-11F0999F7F3F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="28">
   <si>
     <t>Technology_ID</t>
   </si>
@@ -679,6 +679,9 @@
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="B6" s="3" t="s">
         <v>26</v>
       </c>
@@ -696,6 +699,9 @@
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>14</v>
+      </c>
       <c r="B7" s="3" t="s">
         <v>15</v>
       </c>

--- a/data/masterdata/Technology_Rules.xlsx
+++ b/data/masterdata/Technology_Rules.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tora\GitHub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD46E5A8-A0E6-42BD-BF9F-1C4A63D62629}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2F72D33-C67B-4041-80E2-65CD1CED3BB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2280" yWindow="2280" windowWidth="14400" windowHeight="8350" xr2:uid="{34F0C614-9941-4C4B-8976-11F0999F7F3F}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{34F0C614-9941-4C4B-8976-11F0999F7F3F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="28">
   <si>
     <t>Technology_ID</t>
   </si>
@@ -677,6 +677,9 @@
       <c r="I5" s="3">
         <v>30</v>
       </c>
+      <c r="J5" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
@@ -688,14 +691,26 @@
       <c r="C6" s="3" t="s">
         <v>27</v>
       </c>
+      <c r="D6" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
       <c r="F6" s="3">
         <v>1000</v>
       </c>
       <c r="G6" s="3">
         <v>10000000</v>
       </c>
+      <c r="H6" s="3" t="s">
+        <v>13</v>
+      </c>
       <c r="I6" s="3">
         <v>100</v>
+      </c>
+      <c r="J6" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
@@ -708,14 +723,26 @@
       <c r="C7" s="3" t="s">
         <v>27</v>
       </c>
+      <c r="D7" s="3" t="s">
+        <v>23</v>
+      </c>
       <c r="E7" s="3">
         <v>1</v>
       </c>
       <c r="F7" s="3">
         <v>5000</v>
       </c>
+      <c r="G7">
+        <v>5000</v>
+      </c>
+      <c r="H7" t="s">
+        <v>17</v>
+      </c>
       <c r="I7" s="3">
         <v>80</v>
+      </c>
+      <c r="J7" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.35">

--- a/data/masterdata/Technology_Rules.xlsx
+++ b/data/masterdata/Technology_Rules.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tora\GitHub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2F72D33-C67B-4041-80E2-65CD1CED3BB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29C2A485-FFF9-4701-8865-CC16DB1C7318}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{34F0C614-9941-4C4B-8976-11F0999F7F3F}"/>
+    <workbookView xWindow="-57720" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{34F0C614-9941-4C4B-8976-11F0999F7F3F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="26">
   <si>
     <t>Technology_ID</t>
   </si>
@@ -117,12 +117,6 @@
   </si>
   <si>
     <t>Injection Molding</t>
-  </si>
-  <si>
-    <t>Injection Moulding</t>
-  </si>
-  <si>
-    <t>Plastic</t>
   </si>
 </sst>
 </file>
@@ -507,7 +501,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D1DFB5D-AA7C-4EFA-829A-D5E820AAF750}">
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="30.36328125" customWidth="1"/>
@@ -681,83 +675,19 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A6" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="F6" s="3">
-        <v>1000</v>
-      </c>
-      <c r="G6" s="3">
-        <v>10000000</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I6" s="3">
-        <v>100</v>
-      </c>
-      <c r="J6" t="s">
-        <v>21</v>
-      </c>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E7" s="3">
-        <v>1</v>
-      </c>
-      <c r="F7" s="3">
-        <v>5000</v>
-      </c>
-      <c r="G7">
-        <v>5000</v>
-      </c>
-      <c r="H7" t="s">
-        <v>17</v>
-      </c>
-      <c r="I7" s="3">
-        <v>80</v>
-      </c>
-      <c r="J7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/masterdata/Technology_Rules.xlsx
+++ b/data/masterdata/Technology_Rules.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tora\GitHub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29C2A485-FFF9-4701-8865-CC16DB1C7318}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{699DE50C-D508-4AD5-9599-3F3551B2F427}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-57720" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{34F0C614-9941-4C4B-8976-11F0999F7F3F}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="25">
   <si>
     <t>Technology_ID</t>
   </si>
@@ -107,16 +107,13 @@
     <t>Compatible</t>
   </si>
   <si>
-    <t>Not Compatible</t>
-  </si>
-  <si>
-    <t>0.02</t>
-  </si>
-  <si>
     <t>IM</t>
   </si>
   <si>
     <t>Injection Molding</t>
+  </si>
+  <si>
+    <t>0.020</t>
   </si>
 </sst>
 </file>
@@ -158,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -166,6 +163,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -501,114 +504,115 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D1DFB5D-AA7C-4EFA-829A-D5E820AAF750}">
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="30.36328125" customWidth="1"/>
-    <col min="2" max="2" width="25.1796875" customWidth="1"/>
-    <col min="3" max="4" width="14.26953125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.54296875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.81640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.08984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="14.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.26953125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="20.81640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.453125" customWidth="1"/>
-    <col min="10" max="10" width="17.1796875" customWidth="1"/>
+    <col min="9" max="9" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="30.54296875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="4">
         <v>100</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="4">
         <v>1</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="4">
         <v>5000</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="4">
         <v>20</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="3" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+      <c r="A3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="4">
         <v>5</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="4">
         <v>1</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="4">
         <v>5000</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="I3">
-        <v>20</v>
-      </c>
-      <c r="J3" t="s">
-        <v>22</v>
+      <c r="I3" s="4">
+        <v>40</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
@@ -621,57 +625,57 @@
       <c r="C4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E4" s="3">
+      <c r="D4" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" s="4">
         <v>20</v>
       </c>
-      <c r="F4" s="3">
+      <c r="F4" s="4">
         <v>10000</v>
       </c>
-      <c r="G4" s="3">
+      <c r="G4" s="4">
         <v>5000000</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="I4" s="3">
+      <c r="I4" s="4">
         <v>30</v>
       </c>
-      <c r="J4" t="s">
+      <c r="J4" s="3" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="4">
         <v>5</v>
       </c>
-      <c r="F5" s="3">
+      <c r="F5" s="4">
         <v>1000</v>
       </c>
-      <c r="G5" s="3">
+      <c r="G5" s="4">
         <v>10000000</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="I5" s="3">
-        <v>30</v>
-      </c>
-      <c r="J5" t="s">
+      <c r="I5" s="4">
+        <v>100</v>
+      </c>
+      <c r="J5" s="3" t="s">
         <v>21</v>
       </c>
     </row>
@@ -682,13 +686,6 @@
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
